--- a/artfynd/A 54875-2025 artfynd.xlsx
+++ b/artfynd/A 54875-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129573538</v>
       </c>
       <c r="B2" t="n">
-        <v>56917</v>
+        <v>56920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54875-2025 artfynd.xlsx
+++ b/artfynd/A 54875-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129573538</v>
       </c>
       <c r="B2" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54875-2025 artfynd.xlsx
+++ b/artfynd/A 54875-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129573538</v>
       </c>
       <c r="B2" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54875-2025 artfynd.xlsx
+++ b/artfynd/A 54875-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129573538</v>
       </c>
       <c r="B2" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54875-2025 artfynd.xlsx
+++ b/artfynd/A 54875-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129573538</v>
       </c>
       <c r="B2" t="n">
-        <v>56927</v>
+        <v>56930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54875-2025 artfynd.xlsx
+++ b/artfynd/A 54875-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,6 +790,1075 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130095310</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91623</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Storbäcken Robertsfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>779229</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7128243</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130095376</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Storbäcken Robertsfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>779263</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7128330</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>hack i stambasen på en gran</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130095374</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Storbäcken Robertsfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>779304</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7128363</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130095319</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91623</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Storbäcken Robertsfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>779221</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7128273</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130095364</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Storbäcken Robertsfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>779219</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7128307</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>hål hackade i gran</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130095305</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91623</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Storbäcken Robertsfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>779256</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7128219</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130095328</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91643</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Storbäcken Robertsfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>779203</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7128297</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130095339</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Storbäcken Robertsfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>779220</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7128299</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>hack i basen på död gran</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130095369</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Storbäcken Robertsfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>779219</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7128307</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>äldre ringhack på en gran</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130095304</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Storbäcken Robertsfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>779256</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7128219</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>typiska gnagspår i död gran</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54875-2025 artfynd.xlsx
+++ b/artfynd/A 54875-2025 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>130095310</v>
       </c>
       <c r="B3" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>130095374</v>
       </c>
       <c r="B5" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>130095319</v>
       </c>
       <c r="B6" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130095364</v>
+        <v>130095305</v>
       </c>
       <c r="B7" t="n">
-        <v>57738</v>
+        <v>91641</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,31 +1229,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1261,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>779219</v>
+        <v>779256</v>
       </c>
       <c r="R7" t="n">
-        <v>7128307</v>
+        <v>7128219</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,17 +1298,13 @@
           <t>2025-11-20</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>hål hackade i gran</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1328,10 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130095305</v>
+        <v>130095364</v>
       </c>
       <c r="B8" t="n">
-        <v>91639</v>
+        <v>57738</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1339,30 +1334,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1370,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>779256</v>
+        <v>779219</v>
       </c>
       <c r="R8" t="n">
-        <v>7128219</v>
+        <v>7128307</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,13 +1404,17 @@
           <t>2025-11-20</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>hål hackade i gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1436,7 +1436,7 @@
         <v>130095328</v>
       </c>
       <c r="B9" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54875-2025 artfynd.xlsx
+++ b/artfynd/A 54875-2025 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>130095310</v>
       </c>
       <c r="B3" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>130095376</v>
       </c>
       <c r="B4" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>130095374</v>
       </c>
       <c r="B5" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>130095319</v>
       </c>
       <c r="B6" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>130095305</v>
       </c>
       <c r="B7" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>130095364</v>
       </c>
       <c r="B8" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>130095328</v>
       </c>
       <c r="B9" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>130095339</v>
       </c>
       <c r="B10" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>130095369</v>
       </c>
       <c r="B11" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 54875-2025 artfynd.xlsx
+++ b/artfynd/A 54875-2025 artfynd.xlsx
@@ -1218,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130095305</v>
+        <v>130095364</v>
       </c>
       <c r="B7" t="n">
-        <v>91728</v>
+        <v>57823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,30 +1229,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1260,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>779256</v>
+        <v>779219</v>
       </c>
       <c r="R7" t="n">
-        <v>7128219</v>
+        <v>7128307</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,13 +1299,17 @@
           <t>2025-11-20</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>hål hackade i gran</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1323,10 +1328,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130095364</v>
+        <v>130095305</v>
       </c>
       <c r="B8" t="n">
-        <v>57823</v>
+        <v>91728</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1334,31 +1339,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1366,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>779219</v>
+        <v>779256</v>
       </c>
       <c r="R8" t="n">
-        <v>7128307</v>
+        <v>7128219</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,17 +1408,13 @@
           <t>2025-11-20</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>hål hackade i gran</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54875-2025 artfynd.xlsx
+++ b/artfynd/A 54875-2025 artfynd.xlsx
@@ -1218,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130095364</v>
+        <v>130095305</v>
       </c>
       <c r="B7" t="n">
-        <v>57823</v>
+        <v>91728</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,31 +1229,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1261,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>779219</v>
+        <v>779256</v>
       </c>
       <c r="R7" t="n">
-        <v>7128307</v>
+        <v>7128219</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,17 +1298,13 @@
           <t>2025-11-20</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>hål hackade i gran</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1328,10 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130095305</v>
+        <v>130095364</v>
       </c>
       <c r="B8" t="n">
-        <v>91728</v>
+        <v>57823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1339,30 +1334,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1370,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>779256</v>
+        <v>779219</v>
       </c>
       <c r="R8" t="n">
-        <v>7128219</v>
+        <v>7128307</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,13 +1404,17 @@
           <t>2025-11-20</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>hål hackade i gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54875-2025 artfynd.xlsx
+++ b/artfynd/A 54875-2025 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>130095310</v>
       </c>
       <c r="B3" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>130095374</v>
       </c>
       <c r="B5" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>130095319</v>
       </c>
       <c r="B6" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>130095305</v>
       </c>
       <c r="B7" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>130095328</v>
       </c>
       <c r="B9" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54875-2025 artfynd.xlsx
+++ b/artfynd/A 54875-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130095305</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130095310</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130095319</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130095374</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130095339</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1312,6 +1342,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130095364</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1422,6 +1457,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130095376</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1532,6 +1572,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130095369</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1650,6 +1695,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129573538</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1763,6 +1813,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129573539</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1875,8 +1930,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130095304</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>